--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/2_fold/124.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/2_fold/124.xlsx
@@ -426,13 +426,13 @@
         <v>-1.178371872178943</v>
       </c>
       <c r="E2">
-        <v>-23.18838658519858</v>
+        <v>-16.71835616135033</v>
       </c>
       <c r="F2">
-        <v>-1.315403679420774</v>
+        <v>-0.9673883094218404</v>
       </c>
       <c r="G2">
-        <v>-10.60110539867861</v>
+        <v>-10.55532729764573</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-1.66296456146775</v>
       </c>
       <c r="E3">
-        <v>-22.20669202434886</v>
+        <v>-18.09713925696691</v>
       </c>
       <c r="F3">
-        <v>-1.410125006828689</v>
+        <v>-0.6226698416860486</v>
       </c>
       <c r="G3">
-        <v>-10.66075308035177</v>
+        <v>-9.996548327437463</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-2.29292534728599</v>
       </c>
       <c r="E4">
-        <v>-22.82046190035467</v>
+        <v>-18.11352367564336</v>
       </c>
       <c r="F4">
-        <v>-1.670981215439865</v>
+        <v>-0.4777270837486078</v>
       </c>
       <c r="G4">
-        <v>-10.52527110054054</v>
+        <v>-10.01032653201706</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-3.002960295261679</v>
       </c>
       <c r="E5">
-        <v>-24.63231695365642</v>
+        <v>-19.06882042531247</v>
       </c>
       <c r="F5">
-        <v>-1.465939574061917</v>
+        <v>-0.4668522764846559</v>
       </c>
       <c r="G5">
-        <v>-10.78841718548492</v>
+        <v>-10.81795514978877</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-3.769900435120964</v>
       </c>
       <c r="E6">
-        <v>-25.99074931378134</v>
+        <v>-20.210949386429</v>
       </c>
       <c r="F6">
-        <v>-0.8027444895436191</v>
+        <v>-0.2464966069311538</v>
       </c>
       <c r="G6">
-        <v>-10.26806184879636</v>
+        <v>-11.4126775461552</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-4.556442864928059</v>
       </c>
       <c r="E7">
-        <v>-26.41783649394743</v>
+        <v>-21.16106708157605</v>
       </c>
       <c r="F7">
-        <v>-1.906047861699683</v>
+        <v>-0.02669014496570782</v>
       </c>
       <c r="G7">
-        <v>-11.45494680645762</v>
+        <v>-11.32020366736567</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-5.331748067029515</v>
       </c>
       <c r="E8">
-        <v>-26.27318429671498</v>
+        <v>-21.89933362025492</v>
       </c>
       <c r="F8">
-        <v>-0.1334990095152733</v>
+        <v>0.1758233190988957</v>
       </c>
       <c r="G8">
-        <v>-11.29042029307025</v>
+        <v>-11.47498296582212</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-6.050334734574873</v>
       </c>
       <c r="E9">
-        <v>-27.75449356709628</v>
+        <v>-22.22634502033794</v>
       </c>
       <c r="F9">
-        <v>-0.3091915938120344</v>
+        <v>0.7977085496069853</v>
       </c>
       <c r="G9">
-        <v>-11.72462758511355</v>
+        <v>-11.94870126650733</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-6.676535791430815</v>
       </c>
       <c r="E10">
-        <v>-28.58008968030232</v>
+        <v>-23.16851346900927</v>
       </c>
       <c r="F10">
-        <v>-0.6777985207097584</v>
+        <v>0.9137214043690561</v>
       </c>
       <c r="G10">
-        <v>-12.90460059646984</v>
+        <v>-11.62164545934479</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-7.177106356148762</v>
       </c>
       <c r="E11">
-        <v>-30.68505346964252</v>
+        <v>-24.4909499465819</v>
       </c>
       <c r="F11">
-        <v>-0.2048694882056731</v>
+        <v>1.167258158609095</v>
       </c>
       <c r="G11">
-        <v>-10.76958327400463</v>
+        <v>-11.4112076969504</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-7.524241065523931</v>
       </c>
       <c r="E12">
-        <v>-29.83720860336937</v>
+        <v>-23.78155653303324</v>
       </c>
       <c r="F12">
-        <v>1.051271811603914</v>
+        <v>1.405670580808821</v>
       </c>
       <c r="G12">
-        <v>-11.06960351555389</v>
+        <v>-11.6224064913931</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-7.698571103085064</v>
       </c>
       <c r="E13">
-        <v>-33.21381717238521</v>
+        <v>-26.41345485599974</v>
       </c>
       <c r="F13">
-        <v>0.6759310860888328</v>
+        <v>1.940870476083554</v>
       </c>
       <c r="G13">
-        <v>-11.63551895610197</v>
+        <v>-11.39838633026345</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-7.699798236059092</v>
       </c>
       <c r="E14">
-        <v>-30.37886004132519</v>
+        <v>-26.37544466595491</v>
       </c>
       <c r="F14">
-        <v>0.6010574416519939</v>
+        <v>2.323705441491762</v>
       </c>
       <c r="G14">
-        <v>-11.15212654133439</v>
+        <v>-11.1491855375525</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-7.537488754042083</v>
       </c>
       <c r="E15">
-        <v>-32.3241017061408</v>
+        <v>-28.35903708414398</v>
       </c>
       <c r="F15">
-        <v>0.8117758848413266</v>
+        <v>2.365234812863712</v>
       </c>
       <c r="G15">
-        <v>-11.98944454659624</v>
+        <v>-11.0780035862758</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-7.230257492165446</v>
       </c>
       <c r="E16">
-        <v>-34.1329373748094</v>
+        <v>-27.85046597439041</v>
       </c>
       <c r="F16">
-        <v>1.384794065523468</v>
+        <v>2.518656739536209</v>
       </c>
       <c r="G16">
-        <v>-9.443733603247589</v>
+        <v>-9.924359934120885</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-6.816309376645243</v>
       </c>
       <c r="E17">
-        <v>-34.19740767420471</v>
+        <v>-29.98743441019974</v>
       </c>
       <c r="F17">
-        <v>1.92242604749282</v>
+        <v>2.708937702163672</v>
       </c>
       <c r="G17">
-        <v>-9.767741366099997</v>
+        <v>-9.314253725251325</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-6.338991283912518</v>
       </c>
       <c r="E18">
-        <v>-35.49499133520957</v>
+        <v>-30.71324962132678</v>
       </c>
       <c r="F18">
-        <v>1.500886443556207</v>
+        <v>3.359898628510024</v>
       </c>
       <c r="G18">
-        <v>-9.539734597979709</v>
+        <v>-8.068957273480789</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-5.837217032647618</v>
       </c>
       <c r="E19">
-        <v>-36.46816142981508</v>
+        <v>-31.61774429007059</v>
       </c>
       <c r="F19">
-        <v>1.81534962027215</v>
+        <v>3.511580983636642</v>
       </c>
       <c r="G19">
-        <v>-9.258365515789363</v>
+        <v>-7.891059831670034</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-5.356057029557694</v>
       </c>
       <c r="E20">
-        <v>-38.34017367255131</v>
+        <v>-32.67254367665994</v>
       </c>
       <c r="F20">
-        <v>2.378096045159577</v>
+        <v>4.292395127311039</v>
       </c>
       <c r="G20">
-        <v>-7.76587854464304</v>
+        <v>-6.773950939323163</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-4.933914634685177</v>
       </c>
       <c r="E21">
-        <v>-37.62977933507337</v>
+        <v>-33.11891629361288</v>
       </c>
       <c r="F21">
-        <v>2.531910617981001</v>
+        <v>4.401742937950185</v>
       </c>
       <c r="G21">
-        <v>-8.370357293546453</v>
+        <v>-6.665307413908574</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-4.591657238163552</v>
       </c>
       <c r="E22">
-        <v>-38.8567106416259</v>
+        <v>-34.32150978180191</v>
       </c>
       <c r="F22">
-        <v>2.687348790911911</v>
+        <v>4.594986142410059</v>
       </c>
       <c r="G22">
-        <v>-8.032554356274602</v>
+        <v>-6.48702749801522</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-4.343095811357389</v>
       </c>
       <c r="E23">
-        <v>-39.75272860605573</v>
+        <v>-34.33730029125891</v>
       </c>
       <c r="F23">
-        <v>2.530127971330176</v>
+        <v>4.832547002919707</v>
       </c>
       <c r="G23">
-        <v>-5.932152896342958</v>
+        <v>-5.885749521980511</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-4.200019603164725</v>
       </c>
       <c r="E24">
-        <v>-40.92064070307679</v>
+        <v>-35.91110988426679</v>
       </c>
       <c r="F24">
-        <v>4.036295404326738</v>
+        <v>5.039885707105618</v>
       </c>
       <c r="G24">
-        <v>-6.805527895152677</v>
+        <v>-4.398322173851765</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-4.156664510240561</v>
       </c>
       <c r="E25">
-        <v>-38.74736489386581</v>
+        <v>-36.58123260813354</v>
       </c>
       <c r="F25">
-        <v>3.464977033555142</v>
+        <v>4.731429850794777</v>
       </c>
       <c r="G25">
-        <v>-6.397395414713119</v>
+        <v>-4.609980459342502</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-4.196671007416788</v>
       </c>
       <c r="E26">
-        <v>-41.05151462173913</v>
+        <v>-35.95622206567708</v>
       </c>
       <c r="F26">
-        <v>3.43340132489523</v>
+        <v>5.868884325866056</v>
       </c>
       <c r="G26">
-        <v>-5.327021461291766</v>
+        <v>-4.209761145758608</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-4.314847190746256</v>
       </c>
       <c r="E27">
-        <v>-41.36055922963094</v>
+        <v>-36.9712710666765</v>
       </c>
       <c r="F27">
-        <v>3.559543456258733</v>
+        <v>5.643835126608292</v>
       </c>
       <c r="G27">
-        <v>-6.94677700976568</v>
+        <v>-5.130991092923433</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-4.493424870935611</v>
       </c>
       <c r="E28">
-        <v>-42.00860971191189</v>
+        <v>-37.45996283042378</v>
       </c>
       <c r="F28">
-        <v>3.657237794275296</v>
+        <v>5.143628783897422</v>
       </c>
       <c r="G28">
-        <v>-5.896586722778222</v>
+        <v>-5.332856475452904</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-4.707271667830197</v>
       </c>
       <c r="E29">
-        <v>-41.05683903865756</v>
+        <v>-36.93398561200785</v>
       </c>
       <c r="F29">
-        <v>3.730790192704669</v>
+        <v>5.043275386517873</v>
       </c>
       <c r="G29">
-        <v>-6.723109299155822</v>
+        <v>-4.053145188482314</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-4.944924075666878</v>
       </c>
       <c r="E30">
-        <v>-41.57190992413448</v>
+        <v>-36.86648762155674</v>
       </c>
       <c r="F30">
-        <v>3.40553670219986</v>
+        <v>4.844773705785028</v>
       </c>
       <c r="G30">
-        <v>-5.654531538013154</v>
+        <v>-5.209582337349717</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-5.190240558374428</v>
       </c>
       <c r="E31">
-        <v>-42.27040323456114</v>
+        <v>-36.41597009970162</v>
       </c>
       <c r="F31">
-        <v>3.436868870843349</v>
+        <v>4.762766989642683</v>
       </c>
       <c r="G31">
-        <v>-6.290973632945569</v>
+        <v>-4.636140120145457</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-5.420927998909166</v>
       </c>
       <c r="E32">
-        <v>-40.57611728744263</v>
+        <v>-36.42500333433313</v>
       </c>
       <c r="F32">
-        <v>2.069882072130354</v>
+        <v>4.1710359893313</v>
       </c>
       <c r="G32">
-        <v>-8.266396138556027</v>
+        <v>-5.000863750268574</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-5.62541787359129</v>
       </c>
       <c r="E33">
-        <v>-39.4381768399472</v>
+        <v>-36.27208832316992</v>
       </c>
       <c r="F33">
-        <v>2.614669491725088</v>
+        <v>4.173325596832638</v>
       </c>
       <c r="G33">
-        <v>-5.9647506533076</v>
+        <v>-4.80585940452455</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-5.793405145201596</v>
       </c>
       <c r="E34">
-        <v>-40.56314265526387</v>
+        <v>-35.54765820801972</v>
       </c>
       <c r="F34">
-        <v>2.946639385131796</v>
+        <v>4.373044977647599</v>
       </c>
       <c r="G34">
-        <v>-4.617820525349615</v>
+        <v>-5.570601320898044</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-5.911034607683404</v>
       </c>
       <c r="E35">
-        <v>-39.60242388821019</v>
+        <v>-34.83869465184318</v>
       </c>
       <c r="F35">
-        <v>2.226238076143567</v>
+        <v>4.148921893146165</v>
       </c>
       <c r="G35">
-        <v>-5.871570568106175</v>
+        <v>-4.660649790366828</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-5.969403981610888</v>
       </c>
       <c r="E36">
-        <v>-40.17819395719948</v>
+        <v>-35.30950891744273</v>
       </c>
       <c r="F36">
-        <v>2.053049646505468</v>
+        <v>3.63479235112904</v>
       </c>
       <c r="G36">
-        <v>-5.592609897801129</v>
+        <v>-4.834859555442636</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-5.967101462358536</v>
       </c>
       <c r="E37">
-        <v>-38.89483089177084</v>
+        <v>-34.06220403273625</v>
       </c>
       <c r="F37">
-        <v>2.134173322996429</v>
+        <v>3.644630042404687</v>
       </c>
       <c r="G37">
-        <v>-6.522789477424291</v>
+        <v>-4.394387781752958</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-5.899980410378532</v>
       </c>
       <c r="E38">
-        <v>-39.92118493399644</v>
+        <v>-33.44083793321732</v>
       </c>
       <c r="F38">
-        <v>1.874866161428489</v>
+        <v>3.390869628965892</v>
       </c>
       <c r="G38">
-        <v>-5.220907747385966</v>
+        <v>-4.3114705335392</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-5.764351548372233</v>
       </c>
       <c r="E39">
-        <v>-41.33384577438965</v>
+        <v>-32.64265093814949</v>
       </c>
       <c r="F39">
-        <v>1.696957694329239</v>
+        <v>2.904858190069394</v>
       </c>
       <c r="G39">
-        <v>-5.779975204871556</v>
+        <v>-4.636487349176075</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-5.567967387048384</v>
       </c>
       <c r="E40">
-        <v>-38.75689028403931</v>
+        <v>-31.65390837768153</v>
       </c>
       <c r="F40">
-        <v>2.00965976194683</v>
+        <v>3.085510210006716</v>
       </c>
       <c r="G40">
-        <v>-5.574292913749878</v>
+        <v>-4.10909083432528</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-5.315950995795555</v>
       </c>
       <c r="E41">
-        <v>-36.94063075012757</v>
+        <v>-32.85842895592529</v>
       </c>
       <c r="F41">
-        <v>1.167143843907509</v>
+        <v>2.600999772844091</v>
       </c>
       <c r="G41">
-        <v>-4.354252805153774</v>
+        <v>-3.869607232982458</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-5.012568484790259</v>
       </c>
       <c r="E42">
-        <v>-37.15886123919069</v>
+        <v>-32.11990907135561</v>
       </c>
       <c r="F42">
-        <v>1.58476527002888</v>
+        <v>2.747471697007099</v>
       </c>
       <c r="G42">
-        <v>-5.058929320719525</v>
+        <v>-3.416131340484445</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-4.671132684664748</v>
       </c>
       <c r="E43">
-        <v>-37.02586295293571</v>
+        <v>-31.46640542260516</v>
       </c>
       <c r="F43">
-        <v>1.221116950404314</v>
+        <v>2.652620315916945</v>
       </c>
       <c r="G43">
-        <v>-4.28726893117958</v>
+        <v>-3.72576303824589</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-4.302899853257052</v>
       </c>
       <c r="E44">
-        <v>-36.0263552687138</v>
+        <v>-31.44497900538037</v>
       </c>
       <c r="F44">
-        <v>1.697691627848119</v>
+        <v>2.237621500992837</v>
       </c>
       <c r="G44">
-        <v>-3.547007966836954</v>
+        <v>-3.414207221720795</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-3.914973498646422</v>
       </c>
       <c r="E45">
-        <v>-37.15275809514885</v>
+        <v>-30.67746970576338</v>
       </c>
       <c r="F45">
-        <v>1.285027152265101</v>
+        <v>2.756136420040382</v>
       </c>
       <c r="G45">
-        <v>-3.688492048463157</v>
+        <v>-3.816663943419272</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-3.518653989842421</v>
       </c>
       <c r="E46">
-        <v>-36.55809299123726</v>
+        <v>-31.28014220110925</v>
       </c>
       <c r="F46">
-        <v>1.790165594492239</v>
+        <v>2.078301598412408</v>
       </c>
       <c r="G46">
-        <v>-4.833705606333364</v>
+        <v>-2.906798567459563</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-3.126403012323129</v>
       </c>
       <c r="E47">
-        <v>-35.85577872639176</v>
+        <v>-29.55071593297137</v>
       </c>
       <c r="F47">
-        <v>1.68751596267213</v>
+        <v>2.462248232875174</v>
       </c>
       <c r="G47">
-        <v>-3.587866119687877</v>
+        <v>-2.78841174323094</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-2.74577962006895</v>
       </c>
       <c r="E48">
-        <v>-35.11472330630827</v>
+        <v>-29.15210939946529</v>
       </c>
       <c r="F48">
-        <v>0.509735734065168</v>
+        <v>2.396018602286548</v>
       </c>
       <c r="G48">
-        <v>-4.897433881802439</v>
+        <v>-3.21875643865169</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-2.384378798553196</v>
       </c>
       <c r="E49">
-        <v>-35.01306722931611</v>
+        <v>-28.6159422770639</v>
       </c>
       <c r="F49">
-        <v>0.8035038079569707</v>
+        <v>2.301665898372878</v>
       </c>
       <c r="G49">
-        <v>-4.29688430350865</v>
+        <v>-3.193722008767504</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-2.054899752903546</v>
       </c>
       <c r="E50">
-        <v>-34.64852533509627</v>
+        <v>-28.61013401102613</v>
       </c>
       <c r="F50">
-        <v>1.014493955654422</v>
+        <v>2.234848126928264</v>
       </c>
       <c r="G50">
-        <v>-4.194869458610898</v>
+        <v>-3.021099576403094</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-1.763377255889646</v>
       </c>
       <c r="E51">
-        <v>-34.30467681630238</v>
+        <v>-27.09946153657829</v>
       </c>
       <c r="F51">
-        <v>1.073226861247712</v>
+        <v>2.399115039638212</v>
       </c>
       <c r="G51">
-        <v>-4.000415979975599</v>
+        <v>-3.526249936593012</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-1.511750591748553</v>
       </c>
       <c r="E52">
-        <v>-32.63016638490706</v>
+        <v>-27.435252825402</v>
       </c>
       <c r="F52">
-        <v>0.7404733322779563</v>
+        <v>2.111582087187281</v>
       </c>
       <c r="G52">
-        <v>-3.716883895891514</v>
+        <v>-3.349836703082306</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-1.307564704308332</v>
       </c>
       <c r="E53">
-        <v>-29.92298487686105</v>
+        <v>-27.09793730802208</v>
       </c>
       <c r="F53">
-        <v>1.046165754933058</v>
+        <v>2.133378090289742</v>
       </c>
       <c r="G53">
-        <v>-4.821380281118718</v>
+        <v>-3.298271886663227</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-1.15070442353213</v>
       </c>
       <c r="E54">
-        <v>-32.48485590367962</v>
+        <v>-26.50358784817116</v>
       </c>
       <c r="F54">
-        <v>0.532608614791268</v>
+        <v>1.783144352386111</v>
       </c>
       <c r="G54">
-        <v>-3.634146789054542</v>
+        <v>-3.218320444304974</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-1.036229256553807</v>
       </c>
       <c r="E55">
-        <v>-31.58609266656407</v>
+        <v>-25.44934914511066</v>
       </c>
       <c r="F55">
-        <v>0.7629088350153781</v>
+        <v>1.448010095500709</v>
       </c>
       <c r="G55">
-        <v>-3.448063357578352</v>
+        <v>-4.058364066919949</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-0.9622300907982287</v>
       </c>
       <c r="E56">
-        <v>-29.68135519519385</v>
+        <v>-24.60576547365679</v>
       </c>
       <c r="F56">
-        <v>0.3467387085837121</v>
+        <v>1.781351765326453</v>
       </c>
       <c r="G56">
-        <v>-3.980519495446724</v>
+        <v>-3.789770663386214</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-0.9227161147518771</v>
       </c>
       <c r="E57">
-        <v>-30.52320282431395</v>
+        <v>-24.2082699241801</v>
       </c>
       <c r="F57">
-        <v>0.5449007586814099</v>
+        <v>1.485747200902644</v>
       </c>
       <c r="G57">
-        <v>-3.096547484341677</v>
+        <v>-4.076926460962764</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-0.9074838455272503</v>
       </c>
       <c r="E58">
-        <v>-29.2302541471476</v>
+        <v>-24.48905608221778</v>
       </c>
       <c r="F58">
-        <v>0.9919076900496903</v>
+        <v>1.436896718424751</v>
       </c>
       <c r="G58">
-        <v>-4.775076115050733</v>
+        <v>-4.814451364973904</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-0.9075613397786166</v>
       </c>
       <c r="E59">
-        <v>-28.38581491416081</v>
+        <v>-23.46702968619265</v>
       </c>
       <c r="F59">
-        <v>0.5168124767872843</v>
+        <v>1.174284370919641</v>
       </c>
       <c r="G59">
-        <v>-4.594490911683427</v>
+        <v>-4.826714032318362</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-0.9143307963262834</v>
       </c>
       <c r="E60">
-        <v>-29.03310535876932</v>
+        <v>-22.99103013625405</v>
       </c>
       <c r="F60">
-        <v>-0.221479082999206</v>
+        <v>1.45592266093225</v>
       </c>
       <c r="G60">
-        <v>-3.823018495754042</v>
+        <v>-4.525635133837405</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-0.9179114984441497</v>
       </c>
       <c r="E61">
-        <v>-29.62841421043626</v>
+        <v>-22.46162859510081</v>
       </c>
       <c r="F61">
-        <v>0.8513287715901974</v>
+        <v>0.8719667170635442</v>
       </c>
       <c r="G61">
-        <v>-5.773103725107746</v>
+        <v>-4.68065853691312</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-0.9095385445953444</v>
       </c>
       <c r="E62">
-        <v>-29.2829293263804</v>
+        <v>-22.5454320932132</v>
       </c>
       <c r="F62">
-        <v>0.8857358400328776</v>
+        <v>1.086295185394277</v>
       </c>
       <c r="G62">
-        <v>-5.096524042831556</v>
+        <v>-5.132996144769408</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-0.8824397990365677</v>
       </c>
       <c r="E63">
-        <v>-28.14475214583945</v>
+        <v>-20.39976683288968</v>
       </c>
       <c r="F63">
-        <v>0.06979229154055899</v>
+        <v>0.3388410537654216</v>
       </c>
       <c r="G63">
-        <v>-5.352131602769093</v>
+        <v>-5.548013158695732</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-0.8292530625938831</v>
       </c>
       <c r="E64">
-        <v>-26.18885334076434</v>
+        <v>-21.00496448072104</v>
       </c>
       <c r="F64">
-        <v>0.07549725784363918</v>
+        <v>0.2439838741034474</v>
       </c>
       <c r="G64">
-        <v>-4.59940172225931</v>
+        <v>-6.215713698617546</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-0.7439145283213142</v>
       </c>
       <c r="E65">
-        <v>-24.33719391012543</v>
+        <v>-20.68400430953829</v>
       </c>
       <c r="F65">
-        <v>-0.01256068217615666</v>
+        <v>0.4400940581444108</v>
       </c>
       <c r="G65">
-        <v>-7.237527802644193</v>
+        <v>-5.581759643280463</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-0.6210001001438475</v>
       </c>
       <c r="E66">
-        <v>-26.26284280051615</v>
+        <v>-20.79379860412146</v>
       </c>
       <c r="F66">
-        <v>-0.413496303702937</v>
+        <v>-0.0947471540449096</v>
       </c>
       <c r="G66">
-        <v>-6.287381248388197</v>
+        <v>-5.76044944607462</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-0.4558798162380736</v>
       </c>
       <c r="E67">
-        <v>-28.65895085693816</v>
+        <v>-20.02281306662559</v>
       </c>
       <c r="F67">
-        <v>-0.8319618362077604</v>
+        <v>0.05572992651063459</v>
       </c>
       <c r="G67">
-        <v>-5.319727040904195</v>
+        <v>-5.69147879546659</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-0.2484701311765292</v>
       </c>
       <c r="E68">
-        <v>-28.26997354388869</v>
+        <v>-20.75525264981573</v>
       </c>
       <c r="F68">
-        <v>-0.5345464606414315</v>
+        <v>-0.09514891223526736</v>
       </c>
       <c r="G68">
-        <v>-6.773120722543188</v>
+        <v>-6.043206139015145</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>0.001889250945868613</v>
       </c>
       <c r="E69">
-        <v>-25.81851979335202</v>
+        <v>-20.13919850758126</v>
       </c>
       <c r="F69">
-        <v>-1.027415124898304</v>
+        <v>-0.9600580862744675</v>
       </c>
       <c r="G69">
-        <v>-5.862033518114838</v>
+        <v>-5.895252632292164</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>0.2933800090776699</v>
       </c>
       <c r="E70">
-        <v>-26.78787101014435</v>
+        <v>-19.54941342697633</v>
       </c>
       <c r="F70">
-        <v>-1.074429945211592</v>
+        <v>-0.6826221040962599</v>
       </c>
       <c r="G70">
-        <v>-6.258524688422622</v>
+        <v>-5.505669492172466</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>0.619870457403485</v>
       </c>
       <c r="E71">
-        <v>-25.24430094879255</v>
+        <v>-19.77725860025643</v>
       </c>
       <c r="F71">
-        <v>-0.9624040227591958</v>
+        <v>-1.075366000376756</v>
       </c>
       <c r="G71">
-        <v>-5.493863705131451</v>
+        <v>-5.879585554000893</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>0.9771487839409981</v>
       </c>
       <c r="E72">
-        <v>-25.70410297456432</v>
+        <v>-19.37409807053267</v>
       </c>
       <c r="F72">
-        <v>-1.435770433251959</v>
+        <v>-0.7281375794104816</v>
       </c>
       <c r="G72">
-        <v>-5.970865017139986</v>
+        <v>-5.535515524338073</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>1.360698710440889</v>
       </c>
       <c r="E73">
-        <v>-27.11518144144277</v>
+        <v>-19.38810685233132</v>
       </c>
       <c r="F73">
-        <v>-1.767535719910175</v>
+        <v>-0.7345806210694561</v>
       </c>
       <c r="G73">
-        <v>-4.955178330668683</v>
+        <v>-5.152286936553145</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>1.762789531392779</v>
       </c>
       <c r="E74">
-        <v>-27.55858243569279</v>
+        <v>-20.89084669314873</v>
       </c>
       <c r="F74">
-        <v>-2.136925454003545</v>
+        <v>-1.178517622842962</v>
       </c>
       <c r="G74">
-        <v>-4.87203916916468</v>
+        <v>-4.44664183474409</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>2.175984263036144</v>
       </c>
       <c r="E75">
-        <v>-26.34654246834543</v>
+        <v>-20.14632126500334</v>
       </c>
       <c r="F75">
-        <v>-1.067181730437097</v>
+        <v>-1.181875824293911</v>
       </c>
       <c r="G75">
-        <v>-4.089755659883495</v>
+        <v>-4.450787697154778</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>2.595794026605724</v>
       </c>
       <c r="E76">
-        <v>-26.93201651559518</v>
+        <v>-20.50311534349671</v>
       </c>
       <c r="F76">
-        <v>-1.796100313060911</v>
+        <v>-1.657769583732616</v>
       </c>
       <c r="G76">
-        <v>-3.603642849251975</v>
+        <v>-3.953524396374613</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>3.01648508881802</v>
       </c>
       <c r="E77">
-        <v>-25.38386130894077</v>
+        <v>-21.10533513880817</v>
       </c>
       <c r="F77">
-        <v>-1.645607493524713</v>
+        <v>-1.378373684279384</v>
       </c>
       <c r="G77">
-        <v>-3.835082746509576</v>
+        <v>-3.03356588182566</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>3.430594758997474</v>
       </c>
       <c r="E78">
-        <v>-27.63217318715742</v>
+        <v>-21.42680615498388</v>
       </c>
       <c r="F78">
-        <v>-2.185268147263521</v>
+        <v>-1.463239924696194</v>
       </c>
       <c r="G78">
-        <v>-2.74744393910719</v>
+        <v>-3.027639491603833</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>3.836823806853888</v>
       </c>
       <c r="E79">
-        <v>-27.55058335068117</v>
+        <v>-21.60896185047953</v>
       </c>
       <c r="F79">
-        <v>-2.583012897554718</v>
+        <v>-1.635745779594385</v>
       </c>
       <c r="G79">
-        <v>-1.640415131626606</v>
+        <v>-2.38735699137789</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>4.230974509612503</v>
       </c>
       <c r="E80">
-        <v>-27.58088518050712</v>
+        <v>-22.27094635675528</v>
       </c>
       <c r="F80">
-        <v>-1.809633351320446</v>
+        <v>-1.961624687488308</v>
       </c>
       <c r="G80">
-        <v>-2.334390205113384</v>
+        <v>-1.92844813938577</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>4.60181058619368</v>
       </c>
       <c r="E81">
-        <v>-30.61164753608183</v>
+        <v>-22.60187423511762</v>
       </c>
       <c r="F81">
-        <v>-2.298455440814643</v>
+        <v>-1.633910945797184</v>
       </c>
       <c r="G81">
-        <v>-1.409881162742121</v>
+        <v>-1.566152501732389</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>4.945001417257942</v>
       </c>
       <c r="E82">
-        <v>-27.41929203428069</v>
+        <v>-23.58753926599388</v>
       </c>
       <c r="F82">
-        <v>-2.733538851787027</v>
+        <v>-1.44108192503871</v>
       </c>
       <c r="G82">
-        <v>-1.827328779882771</v>
+        <v>-1.131014479242355</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>5.252932723008191</v>
       </c>
       <c r="E83">
-        <v>-28.9589331577192</v>
+        <v>-24.48329973132157</v>
       </c>
       <c r="F83">
-        <v>-2.715553338737444</v>
+        <v>-1.661160091512274</v>
       </c>
       <c r="G83">
-        <v>-0.6785985490483338</v>
+        <v>-0.2609838442538527</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>5.513564215720078</v>
       </c>
       <c r="E84">
-        <v>-32.31481927882981</v>
+        <v>-25.39965181839776</v>
       </c>
       <c r="F84">
-        <v>-2.388566903625978</v>
+        <v>-1.739645417825319</v>
       </c>
       <c r="G84">
-        <v>-0.319226945336999</v>
+        <v>-0.5009922052594882</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>5.718795567326871</v>
       </c>
       <c r="E85">
-        <v>-33.14126680035744</v>
+        <v>-26.9042190721981</v>
       </c>
       <c r="F85">
-        <v>-2.094725105035327</v>
+        <v>-1.564342994575276</v>
       </c>
       <c r="G85">
-        <v>-0.407493609217948</v>
+        <v>-0.3888241746468969</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>5.861765838435475</v>
       </c>
       <c r="E86">
-        <v>-32.27987623534836</v>
+        <v>-27.52400279820226</v>
       </c>
       <c r="F86">
-        <v>-2.23029157234048</v>
+        <v>-1.519099223769173</v>
       </c>
       <c r="G86">
-        <v>-0.0433156247143736</v>
+        <v>0.405421766350769</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>5.932390400067513</v>
       </c>
       <c r="E87">
-        <v>-33.76015758592676</v>
+        <v>-29.34845869466355</v>
       </c>
       <c r="F87">
-        <v>-2.206003840090399</v>
+        <v>-1.590335506940319</v>
       </c>
       <c r="G87">
-        <v>-0.2153558610349658</v>
+        <v>0.4782954801225142</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>5.920948710427331</v>
       </c>
       <c r="E88">
-        <v>-34.15490370950642</v>
+        <v>-30.39613324722515</v>
       </c>
       <c r="F88">
-        <v>-2.901519335563725</v>
+        <v>-1.680094085238062</v>
       </c>
       <c r="G88">
-        <v>-1.276952491140997</v>
+        <v>0.2222205969031676</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>5.824022026833362</v>
       </c>
       <c r="E89">
-        <v>-35.70399961852591</v>
+        <v>-31.56856403816763</v>
       </c>
       <c r="F89">
-        <v>-2.816839477812545</v>
+        <v>-1.396855389403244</v>
       </c>
       <c r="G89">
-        <v>-0.4667261825011263</v>
+        <v>0.08007077540623139</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>5.636723742309695</v>
       </c>
       <c r="E90">
-        <v>-38.02375919116358</v>
+        <v>-33.99362828394634</v>
       </c>
       <c r="F90">
-        <v>-2.36780718814442</v>
+        <v>-1.464708620101357</v>
       </c>
       <c r="G90">
-        <v>0.3194864973896842</v>
+        <v>0.5864951789566132</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>5.355193495203632</v>
       </c>
       <c r="E91">
-        <v>-37.48737402516765</v>
+        <v>-35.06149159675794</v>
       </c>
       <c r="F91">
-        <v>-2.752641004095584</v>
+        <v>-1.652296560302319</v>
       </c>
       <c r="G91">
-        <v>-0.3985491982487939</v>
+        <v>-0.160073344318142</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>4.982380821312294</v>
       </c>
       <c r="E92">
-        <v>-38.50428158823492</v>
+        <v>-35.71829497190596</v>
       </c>
       <c r="F92">
-        <v>-2.535409936385441</v>
+        <v>-1.396655752859169</v>
       </c>
       <c r="G92">
-        <v>-1.128596929750984</v>
+        <v>0.1534901347975192</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>4.520411094764457</v>
       </c>
       <c r="E93">
-        <v>-41.54786283056372</v>
+        <v>-38.85338807256604</v>
       </c>
       <c r="F93">
-        <v>-2.265099570606115</v>
+        <v>-1.405563187541472</v>
       </c>
       <c r="G93">
-        <v>-2.200526886948642</v>
+        <v>0.06395725978988019</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>3.973104885053379</v>
       </c>
       <c r="E94">
-        <v>-41.67710246056974</v>
+        <v>-39.85164148696785</v>
       </c>
       <c r="F94">
-        <v>-2.323166468807555</v>
+        <v>-1.104981791761644</v>
       </c>
       <c r="G94">
-        <v>-0.6823945716838126</v>
+        <v>0.06795692050346575</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>3.349684794804146</v>
       </c>
       <c r="E95">
-        <v>-42.12083155851442</v>
+        <v>-42.22173175104547</v>
       </c>
       <c r="F95">
-        <v>-3.468301566437591</v>
+        <v>-0.5617939496217157</v>
       </c>
       <c r="G95">
-        <v>-2.162007961251356</v>
+        <v>-1.293564658974251</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>2.653476428062636</v>
       </c>
       <c r="E96">
-        <v>-46.56962900993668</v>
+        <v>-44.18252303906123</v>
       </c>
       <c r="F96">
-        <v>-3.49781712536674</v>
+        <v>-0.8967095175127782</v>
       </c>
       <c r="G96">
-        <v>-2.572080224922111</v>
+        <v>-0.8553955620139345</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>1.903025137742568</v>
       </c>
       <c r="E97">
-        <v>-48.04547576912299</v>
+        <v>-44.7827264502745</v>
       </c>
       <c r="F97">
-        <v>-3.151295301795054</v>
+        <v>-0.5886115159199469</v>
       </c>
       <c r="G97">
-        <v>-2.282582589447332</v>
+        <v>-1.489521926494032</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>1.091391111943312</v>
       </c>
       <c r="E98">
-        <v>-50.00052316587652</v>
+        <v>-48.04931852790128</v>
       </c>
       <c r="F98">
-        <v>-2.28454135354982</v>
+        <v>-0.348427215845633</v>
       </c>
       <c r="G98">
-        <v>-3.104852262886008</v>
+        <v>-2.064219911846617</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>0.2590242465031877</v>
       </c>
       <c r="E99">
-        <v>-50.92938887867442</v>
+        <v>-49.64955811947754</v>
       </c>
       <c r="F99">
-        <v>-1.676276968245962</v>
+        <v>-0.28309802062385</v>
       </c>
       <c r="G99">
-        <v>-4.486573173265168</v>
+        <v>-2.115536707529539</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-0.6237378541753072</v>
       </c>
       <c r="E100">
-        <v>-51.9959138191366</v>
+        <v>-51.23284222582019</v>
       </c>
       <c r="F100">
-        <v>-2.011348269208751</v>
+        <v>-0.2172767751648041</v>
       </c>
       <c r="G100">
-        <v>-3.783614527640369</v>
+        <v>-3.389543517568547</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-1.479245782648433</v>
       </c>
       <c r="E101">
-        <v>-52.85529630647012</v>
+        <v>-54.44850139636495</v>
       </c>
       <c r="F101">
-        <v>-0.6280981332765937</v>
+        <v>0.381428250310747</v>
       </c>
       <c r="G101">
-        <v>-5.059143401775996</v>
+        <v>-2.746866964552555</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-2.402831608919939</v>
       </c>
       <c r="E102">
-        <v>-57.35378693139394</v>
+        <v>-55.65412257560978</v>
       </c>
       <c r="F102">
-        <v>-1.853137550580671</v>
+        <v>0.5826395208181497</v>
       </c>
       <c r="G102">
-        <v>-4.730098207235033</v>
+        <v>-3.841805413831693</v>
       </c>
     </row>
   </sheetData>
